--- a/output/result/voting/qwen3-32b-core-All-Avg64ofB128-AllAblation-ssc.xlsx
+++ b/output/result/voting/qwen3-32b-core-All-Avg64ofB128-AllAblation-ssc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.65625</v>
+        <v>0.6567708333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7253331218274112</v>
+        <v>0.7282677664974619</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9041666666666667</v>
+        <v>0.9015625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7786458333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="F2" t="n">
         <v>0.9333333333333333</v>
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6520833333333333</v>
+        <v>0.6447916666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7243020304568528</v>
+        <v>0.7285057106598984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9015625</v>
+        <v>0.9010416666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.8010416666666667</v>
       </c>
       <c r="F3" t="n">
         <v>0.9270833333333334</v>
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.65625</v>
+        <v>0.6552083333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7253331218274112</v>
+        <v>0.7281091370558376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9041666666666667</v>
+        <v>0.9010416666666666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7776041666666667</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="F4" t="n">
         <v>0.9333333333333333</v>
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6473958333333333</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7299333756345178</v>
+        <v>0.7324714467005076</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8927083333333333</v>
+        <v>0.890625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.79375</v>
+        <v>0.7963541666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9322916666666666</v>
       </c>
     </row>
     <row r="6">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6515625</v>
+        <v>0.6473958333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7247779187817259</v>
+        <v>0.7288229695431472</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9005208333333333</v>
+        <v>0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7989583333333333</v>
+        <v>0.8026041666666667</v>
       </c>
       <c r="F6" t="n">
         <v>0.9270833333333334</v>
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6322916666666667</v>
+        <v>0.6338541666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7312817258883249</v>
+        <v>0.7322335025380711</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8921875</v>
+        <v>0.8947916666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0.803125</v>
+        <v>0.7973958333333333</v>
       </c>
       <c r="F7" t="n">
         <v>0.9265625</v>
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6463541666666667</v>
+        <v>0.646875</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7312817258883249</v>
+        <v>0.7314403553299492</v>
       </c>
       <c r="D8" t="n">
-        <v>0.89375</v>
+        <v>0.8916666666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7963541666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9328125</v>
+        <v>0.9322916666666666</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6385416666666667</v>
+        <v>0.6328125</v>
       </c>
       <c r="C9" t="n">
-        <v>0.731757614213198</v>
+        <v>0.7335818527918782</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8911458333333333</v>
+        <v>0.89375</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8005208333333333</v>
+        <v>0.7989583333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.9265625</v>
       </c>
     </row>
     <row r="10">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6411458333333333</v>
+        <v>0.6442708333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7143083756345178</v>
+        <v>0.714863578680203</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8744791666666667</v>
+        <v>0.875</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7755208333333333</v>
+        <v>0.7729166666666667</v>
       </c>
       <c r="F10" t="n">
         <v>0.9333333333333333</v>
@@ -665,85 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.65</v>
+        <v>0.6427083333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7197017766497462</v>
+        <v>0.7216053299492385</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8838541666666667</v>
+        <v>0.8869791666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>0.79375</v>
+        <v>0.790625</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9317708333333333</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.7136738578680203</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8723958333333334</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BoN</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.5807291666666666</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7272366751269036</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8536458333333333</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7640625</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8734375</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MoB-Adaptive</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.63125</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7281091370558376</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8942708333333333</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.803125</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9328125</v>
+        <v>0.9302083333333333</v>
       </c>
     </row>
   </sheetData>
